--- a/data/trans_orig/P62-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P62-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2007</t>
+          <t>Población según si percibe alguna pensión en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154013</t>
+          <t>154135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187581</t>
+          <t>186933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107193</t>
+          <t>106984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146372</t>
+          <t>145496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271926</t>
+          <t>271053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>324874</t>
+          <t>326583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117512</t>
+          <t>118160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151080</t>
+          <t>150958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383755</t>
+          <t>384631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422934</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510347</t>
+          <t>508638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563295</t>
+          <t>564168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204677</t>
+          <t>204448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244465</t>
+          <t>245049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130997</t>
+          <t>131886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177415</t>
+          <t>176263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>348766</t>
+          <t>345850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>412530</t>
+          <t>409874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156312</t>
+          <t>155728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196100</t>
+          <t>196329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>523252</t>
+          <t>524404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>569670</t>
+          <t>568781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>688914</t>
+          <t>691570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752678</t>
+          <t>755594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138722</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171705</t>
+          <t>171611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102800</t>
+          <t>103719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141388</t>
+          <t>140297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253043</t>
+          <t>249713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301389</t>
+          <t>301896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98000</t>
+          <t>98094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130983</t>
+          <t>131319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324806</t>
+          <t>325897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>363394</t>
+          <t>362475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434510</t>
+          <t>434003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482856</t>
+          <t>486186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172207</t>
+          <t>169846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208772</t>
+          <t>208110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155324</t>
+          <t>155002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201530</t>
+          <t>199774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337262</t>
+          <t>338961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398298</t>
+          <t>399616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174996</t>
+          <t>175658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211561</t>
+          <t>213922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448022</t>
+          <t>449778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494228</t>
+          <t>494550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635022</t>
+          <t>633704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696058</t>
+          <t>694359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>704703</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>777999</t>
+          <t>776905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>538793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>619576</t>
+          <t>620420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1262052</t>
+          <t>1264825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1379693</t>
+          <t>1381379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581344</t>
+          <t>582438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>654640</t>
+          <t>653320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1726965</t>
+          <t>1726121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1811530</t>
+          <t>1807748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2326190</t>
+          <t>2324504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2443831</t>
+          <t>2441058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2012</t>
+          <t>Población según si percibe alguna pensión en 2012 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191495</t>
+          <t>191740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233314</t>
+          <t>234056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143565</t>
+          <t>144978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188492</t>
+          <t>187778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347693</t>
+          <t>346980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409777</t>
+          <t>408501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197187</t>
+          <t>196445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239006</t>
+          <t>238761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333439</t>
+          <t>334153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>378366</t>
+          <t>376953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542655</t>
+          <t>543931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>604739</t>
+          <t>605452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>222923</t>
+          <t>223620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272659</t>
+          <t>269545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186607</t>
+          <t>184471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235893</t>
+          <t>235443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>419335</t>
+          <t>422272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>494395</t>
+          <t>492486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329355</t>
+          <t>332469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>379091</t>
+          <t>378394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516669</t>
+          <t>517119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>565955</t>
+          <t>568091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>860181</t>
+          <t>862090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935241</t>
+          <t>932304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146960</t>
+          <t>147115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190094</t>
+          <t>190513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126977</t>
+          <t>127636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172145</t>
+          <t>170408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290151</t>
+          <t>285916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349073</t>
+          <t>345717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242204</t>
+          <t>241785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285338</t>
+          <t>285183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>386723</t>
+          <t>388460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431891</t>
+          <t>431232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642092</t>
+          <t>645448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701014</t>
+          <t>705249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220957</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266636</t>
+          <t>268487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198368</t>
+          <t>202294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>250195</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435918</t>
+          <t>436100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508495</t>
+          <t>504410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249964</t>
+          <t>248113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295643</t>
+          <t>295394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489983</t>
+          <t>488680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>541810</t>
+          <t>537884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748284</t>
+          <t>752369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>820861</t>
+          <t>820679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>822352</t>
+          <t>827419</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>917084</t>
+          <t>915256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>699546</t>
+          <t>705813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>792414</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1556186</t>
+          <t>1555651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1691213</t>
+          <t>1682935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1064329</t>
+          <t>1066157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1159061</t>
+          <t>1153994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1781124</t>
+          <t>1777599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1873992</t>
+          <t>1867725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2863739</t>
+          <t>2872017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2998766</t>
+          <t>2999301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2016</t>
+          <t>Población según si percibe alguna pensión en 2016 (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169843</t>
+          <t>169689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210487</t>
+          <t>210594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128700</t>
+          <t>129193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169890</t>
+          <t>173450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306849</t>
+          <t>308476</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366904</t>
+          <t>368143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215125</t>
+          <t>215018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255769</t>
+          <t>255923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328160</t>
+          <t>324600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369350</t>
+          <t>368857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556758</t>
+          <t>555519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>616813</t>
+          <t>615186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>241909</t>
+          <t>239664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288572</t>
+          <t>289040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>177724</t>
+          <t>177828</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228152</t>
+          <t>229344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>430060</t>
+          <t>434512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>505470</t>
+          <t>504901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313250</t>
+          <t>312782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359913</t>
+          <t>362158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525535</t>
+          <t>524343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>575963</t>
+          <t>575859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>850039</t>
+          <t>850608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925449</t>
+          <t>920997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161958</t>
+          <t>162280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201000</t>
+          <t>201072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114827</t>
+          <t>119261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159059</t>
+          <t>162472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>292860</t>
+          <t>292315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352745</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188926</t>
+          <t>188854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227968</t>
+          <t>227646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>346149</t>
+          <t>342736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390381</t>
+          <t>385947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>542389</t>
+          <t>545133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>602274</t>
+          <t>602819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288113</t>
+          <t>286957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224103</t>
+          <t>223513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277667</t>
+          <t>277261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479725</t>
+          <t>481004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>548847</t>
+          <t>552153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240844</t>
+          <t>242000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286872</t>
+          <t>286930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423663</t>
+          <t>424069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477227</t>
+          <t>477817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681440</t>
+          <t>678134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750562</t>
+          <t>749283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>858465</t>
+          <t>857980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>945068</t>
+          <t>945922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>695881</t>
+          <t>693930</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>792794</t>
+          <t>788550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1583199</t>
+          <t>1575264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1701824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1001248</t>
+          <t>1000394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1087851</t>
+          <t>1088336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1665482</t>
+          <t>1669726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1762395</t>
+          <t>1764346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2694261</t>
+          <t>2702769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2821394</t>
+          <t>2829329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2023</t>
+          <t>Población según si percibe alguna pensión en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159609</t>
+          <t>159285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198689</t>
+          <t>199889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155545</t>
+          <t>155383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186177</t>
+          <t>184295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325393</t>
+          <t>322924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374290</t>
+          <t>373928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102279</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141359</t>
+          <t>141683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228353</t>
+          <t>230235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258985</t>
+          <t>259147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>341208</t>
+          <t>341570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>390105</t>
+          <t>392574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176088</t>
+          <t>175580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>219526</t>
+          <t>220510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165927</t>
+          <t>168609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202427</t>
+          <t>202952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353565</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410652</t>
+          <t>411387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162810</t>
+          <t>161826</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206248</t>
+          <t>206756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348732</t>
+          <t>348207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385232</t>
+          <t>382550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>522844</t>
+          <t>522109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>579931</t>
+          <t>579264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177529</t>
+          <t>177116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225080</t>
+          <t>221212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209446</t>
+          <t>211349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>484548</t>
+          <t>516032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427172</t>
+          <t>426820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>737949</t>
+          <t>733265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119588</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167139</t>
+          <t>167552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121884</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>396986</t>
+          <t>395083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213151</t>
+          <t>217835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>523928</t>
+          <t>524280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197975</t>
+          <t>199465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248026</t>
+          <t>245276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218184</t>
+          <t>218764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258538</t>
+          <t>260804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431759</t>
+          <t>429419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491978</t>
+          <t>490892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204529</t>
+          <t>207279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254580</t>
+          <t>253090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347444</t>
+          <t>345178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387798</t>
+          <t>387218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566559</t>
+          <t>567645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626778</t>
+          <t>629118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>757945</t>
+          <t>757511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>846187</t>
+          <t>850378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>801281</t>
+          <t>803430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1350692</t>
+          <t>1297233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1612998</t>
+          <t>1614534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2158940</t>
+          <t>2133061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>634340</t>
+          <t>630149</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>722582</t>
+          <t>723016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>827411</t>
+          <t>880870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1376822</t>
+          <t>1374673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1499690</t>
+          <t>1525569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2045632</t>
+          <t>2044096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P62-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154135</t>
+          <t>154315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>186933</t>
+          <t>187864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106984</t>
+          <t>106274</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145496</t>
+          <t>145512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271053</t>
+          <t>271809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326583</t>
+          <t>327641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118160</t>
+          <t>117229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150958</t>
+          <t>150778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384631</t>
+          <t>384615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423143</t>
+          <t>423853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508638</t>
+          <t>507580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>564168</t>
+          <t>563412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204448</t>
+          <t>204896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245049</t>
+          <t>245612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>133072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176263</t>
+          <t>176929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>345850</t>
+          <t>349596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>409874</t>
+          <t>411549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155728</t>
+          <t>155165</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196329</t>
+          <t>195881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>524404</t>
+          <t>523738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>568781</t>
+          <t>567595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691570</t>
+          <t>689895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755594</t>
+          <t>751848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138386</t>
+          <t>138913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171611</t>
+          <t>171177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103719</t>
+          <t>103023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140297</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249713</t>
+          <t>247134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301896</t>
+          <t>299565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>98528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131319</t>
+          <t>130792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325897</t>
+          <t>325517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>362475</t>
+          <t>363171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434003</t>
+          <t>436334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>486186</t>
+          <t>488765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>172062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208110</t>
+          <t>211033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155002</t>
+          <t>155058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>198853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338961</t>
+          <t>335909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399616</t>
+          <t>397792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175658</t>
+          <t>172735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213922</t>
+          <t>211706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449778</t>
+          <t>450699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494550</t>
+          <t>494494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633704</t>
+          <t>635528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694359</t>
+          <t>697411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>704978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>776905</t>
+          <t>776480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>538793</t>
+          <t>536304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>620420</t>
+          <t>621544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1264825</t>
+          <t>1267016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1381379</t>
+          <t>1382544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582438</t>
+          <t>582863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>653320</t>
+          <t>654365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1726121</t>
+          <t>1724997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1807748</t>
+          <t>1810237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2324504</t>
+          <t>2323339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2441058</t>
+          <t>2438867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191740</t>
+          <t>191889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>234056</t>
+          <t>233425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144978</t>
+          <t>143848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187778</t>
+          <t>185509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>346980</t>
+          <t>349390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408501</t>
+          <t>413606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196445</t>
+          <t>197076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238761</t>
+          <t>238612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334153</t>
+          <t>336422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376953</t>
+          <t>378083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543931</t>
+          <t>538826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>605452</t>
+          <t>603042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>223620</t>
+          <t>221903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269545</t>
+          <t>271473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184471</t>
+          <t>182485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235443</t>
+          <t>234827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>422272</t>
+          <t>420931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>492486</t>
+          <t>491594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332469</t>
+          <t>330541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378394</t>
+          <t>380111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517119</t>
+          <t>517735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>568091</t>
+          <t>570077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862090</t>
+          <t>862982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932304</t>
+          <t>933645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147115</t>
+          <t>148117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>191241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127636</t>
+          <t>127361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170408</t>
+          <t>170883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285916</t>
+          <t>288160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345717</t>
+          <t>349612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241785</t>
+          <t>241057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285183</t>
+          <t>284181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388460</t>
+          <t>387985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431232</t>
+          <t>431507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645448</t>
+          <t>641553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705249</t>
+          <t>703005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221206</t>
+          <t>221838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268487</t>
+          <t>267049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202294</t>
+          <t>200581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251498</t>
+          <t>250510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>436100</t>
+          <t>437428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>504410</t>
+          <t>509968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248113</t>
+          <t>249551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295394</t>
+          <t>294762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488680</t>
+          <t>489668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537884</t>
+          <t>539597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752369</t>
+          <t>746811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>820679</t>
+          <t>819351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827419</t>
+          <t>827071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>915256</t>
+          <t>916749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>705813</t>
+          <t>700539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>795939</t>
+          <t>796120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1555651</t>
+          <t>1557149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1682935</t>
+          <t>1690707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1066157</t>
+          <t>1064664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1153994</t>
+          <t>1154342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1777599</t>
+          <t>1777418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1867725</t>
+          <t>1872999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2872017</t>
+          <t>2864245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2999301</t>
+          <t>2997803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169689</t>
+          <t>168505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210594</t>
+          <t>211428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129193</t>
+          <t>127555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173450</t>
+          <t>169505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308476</t>
+          <t>310935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368143</t>
+          <t>369959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215018</t>
+          <t>214184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255923</t>
+          <t>257107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324600</t>
+          <t>328545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368857</t>
+          <t>370495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555519</t>
+          <t>553703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>615186</t>
+          <t>612727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239664</t>
+          <t>240069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289040</t>
+          <t>289630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>177828</t>
+          <t>177509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229344</t>
+          <t>229062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>434512</t>
+          <t>430767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>504901</t>
+          <t>507483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312782</t>
+          <t>312192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362158</t>
+          <t>361753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>524343</t>
+          <t>524625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>575859</t>
+          <t>576178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>850608</t>
+          <t>848026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920997</t>
+          <t>924742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162280</t>
+          <t>159179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201072</t>
+          <t>200849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119261</t>
+          <t>117274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162472</t>
+          <t>160496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>292315</t>
+          <t>292930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>350001</t>
+          <t>350787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188854</t>
+          <t>189077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227646</t>
+          <t>230747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>342736</t>
+          <t>344712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>385947</t>
+          <t>387934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545133</t>
+          <t>544347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>602819</t>
+          <t>602204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>243295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286957</t>
+          <t>288688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223513</t>
+          <t>224368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277261</t>
+          <t>277967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481004</t>
+          <t>482412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>552153</t>
+          <t>551302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242000</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286930</t>
+          <t>285662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424069</t>
+          <t>423363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477817</t>
+          <t>476962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678134</t>
+          <t>678985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749283</t>
+          <t>747875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>857980</t>
+          <t>855290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>945922</t>
+          <t>942040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>693930</t>
+          <t>693138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>788550</t>
+          <t>788114</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1575264</t>
+          <t>1582330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1701824</t>
+          <t>1705488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1000394</t>
+          <t>1004276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1088336</t>
+          <t>1091026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1669726</t>
+          <t>1670162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1764346</t>
+          <t>1765138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2702769</t>
+          <t>2699105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2829329</t>
+          <t>2822263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>196624</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159285</t>
+          <t>176388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199889</t>
+          <t>215117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>170085</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155383</t>
+          <t>165107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184295</t>
+          <t>197263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>350049</t>
+          <t>377918</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322924</t>
+          <t>349987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>373928</t>
+          <t>401795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121004</t>
+          <t>124353</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101079</t>
+          <t>105860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141683</t>
+          <t>144589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>244445</t>
+          <t>269107</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230235</t>
+          <t>253138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259147</t>
+          <t>285294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>365449</t>
+          <t>393460</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>341570</t>
+          <t>369583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392574</t>
+          <t>421391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>300968</t>
+          <t>320977</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300968</t>
+          <t>320977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300968</t>
+          <t>320977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>414530</t>
+          <t>450401</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>414530</t>
+          <t>450401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>414530</t>
+          <t>450401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>715498</t>
+          <t>771378</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>715498</t>
+          <t>771378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>715498</t>
+          <t>771378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>198172</t>
+          <t>219541</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175580</t>
+          <t>198388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220510</t>
+          <t>244607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>184788</t>
+          <t>204828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168609</t>
+          <t>185294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202952</t>
+          <t>227058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>382961</t>
+          <t>424370</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>354232</t>
+          <t>393108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>411387</t>
+          <t>453118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>184164</t>
+          <t>196500</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161826</t>
+          <t>171434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206756</t>
+          <t>217653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>366371</t>
+          <t>411231</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348207</t>
+          <t>389001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382550</t>
+          <t>430765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>550535</t>
+          <t>607730</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>522109</t>
+          <t>578982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>579264</t>
+          <t>638992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>382336</t>
+          <t>416041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>382336</t>
+          <t>416041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>382336</t>
+          <t>416041</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>551159</t>
+          <t>616059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>551159</t>
+          <t>616059</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>551159</t>
+          <t>616059</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>933496</t>
+          <t>1032100</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933496</t>
+          <t>1032100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>933496</t>
+          <t>1032100</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>200866</t>
+          <t>226453</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177116</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221212</t>
+          <t>252882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>349752</t>
+          <t>164569</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211349</t>
+          <t>148401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>516032</t>
+          <t>182019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>550618</t>
+          <t>391022</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>426820</t>
+          <t>359695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>733265</t>
+          <t>416995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>143802</t>
+          <t>152354</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>125925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167552</t>
+          <t>176202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>256680</t>
+          <t>305512</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90400</t>
+          <t>288062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>395083</t>
+          <t>321680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>400482</t>
+          <t>457866</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217835</t>
+          <t>431893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>524280</t>
+          <t>489193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>344668</t>
+          <t>378807</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344668</t>
+          <t>378807</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344668</t>
+          <t>378807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>606432</t>
+          <t>470081</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>606432</t>
+          <t>470081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>606432</t>
+          <t>470081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>951100</t>
+          <t>848888</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>951100</t>
+          <t>848888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>951100</t>
+          <t>848888</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>222468</t>
+          <t>231831</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199465</t>
+          <t>205745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245276</t>
+          <t>253230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>238337</t>
+          <t>260073</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218764</t>
+          <t>235830</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260804</t>
+          <t>279817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>460805</t>
+          <t>491905</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429419</t>
+          <t>459556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490892</t>
+          <t>525129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>230087</t>
+          <t>238248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207279</t>
+          <t>216849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253090</t>
+          <t>264334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>367645</t>
+          <t>403444</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345178</t>
+          <t>383700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387218</t>
+          <t>427687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>597732</t>
+          <t>641691</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567645</t>
+          <t>608467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>629118</t>
+          <t>674040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452555</t>
+          <t>470079</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452555</t>
+          <t>470079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452555</t>
+          <t>470079</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>605982</t>
+          <t>663517</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>605982</t>
+          <t>663517</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>605982</t>
+          <t>663517</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1058537</t>
+          <t>1133596</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1058537</t>
+          <t>1133596</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1058537</t>
+          <t>1133596</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>801470</t>
+          <t>874450</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>757511</t>
+          <t>827195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>850378</t>
+          <t>916420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>942962</t>
+          <t>810764</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>803430</t>
+          <t>772622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1297233</t>
+          <t>847928</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1744432</t>
+          <t>1685213</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1614534</t>
+          <t>1622520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2133061</t>
+          <t>1743348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>679057</t>
+          <t>711454</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>630149</t>
+          <t>669484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>723016</t>
+          <t>758709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1235141</t>
+          <t>1389294</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>880870</t>
+          <t>1352130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1374673</t>
+          <t>1427436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1914198</t>
+          <t>2100749</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1525569</t>
+          <t>2042614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2044096</t>
+          <t>2163442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1480527</t>
+          <t>1585904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2178103</t>
+          <t>2200058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3658630</t>
+          <t>3785962</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
